--- a/data/excel/api_cases.xlsx
+++ b/data/excel/api_cases.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="test_login" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="test_message_list" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="test_message_detail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,10 +528,8 @@
           <t>[{"type":"status_code","expected":200},{"type":"json_path_eq","path":"code","expected":200}]</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="L2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -654,4 +653,118 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>headers</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>expected_status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>expected_code</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>asserts</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>use_settings_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>detail_001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>/api/message/index/2267</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>200</v>
+      </c>
+      <c r="J2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>[{"type":"status_code","expected":200},{"type":"json_path_eq","path":"code","expected":200}]</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>